--- a/Team-Data/2009-10/4-12-2009-10.xlsx
+++ b/Team-Data/2009-10/4-12-2009-10.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -679,7 +746,7 @@
         <v>38.7</v>
       </c>
       <c r="J2" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.466</v>
@@ -691,7 +758,7 @@
         <v>17.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O2" t="n">
         <v>17.8</v>
@@ -706,43 +773,43 @@
         <v>11.9</v>
       </c>
       <c r="S2" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T2" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U2" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V2" t="n">
         <v>11.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.5</v>
+        <v>101.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
@@ -757,7 +824,7 @@
         <v>6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK2" t="n">
         <v>11</v>
@@ -769,40 +836,40 @@
         <v>14</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>15</v>
       </c>
       <c r="AR2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>0.615</v>
+        <v>0.625</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.485</v>
+        <v>0.484</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M3" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O3" t="n">
         <v>19.1</v>
@@ -882,13 +949,13 @@
         <v>25.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T3" t="n">
         <v>38.6</v>
@@ -900,10 +967,10 @@
         <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -915,16 +982,16 @@
         <v>21.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="n">
         <v>9</v>
@@ -936,7 +1003,7 @@
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,28 +1012,28 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP3" t="n">
         <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -975,13 +1042,13 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -1028,46 +1095,46 @@
         <v>80</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.538</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="J4" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.456</v>
+        <v>0.453</v>
       </c>
       <c r="L4" t="n">
         <v>5.7</v>
       </c>
       <c r="M4" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="O4" t="n">
         <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.752</v>
+        <v>0.748</v>
       </c>
       <c r="R4" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
         <v>30.4</v>
@@ -1076,40 +1143,40 @@
         <v>40.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W4" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X4" t="n">
         <v>5.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
         <v>15</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>15</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
@@ -1133,40 +1200,40 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>4</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="n">
         <v>19</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
         <v>29</v>
       </c>
       <c r="AW4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
@@ -1175,10 +1242,10 @@
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1297,13 +1364,13 @@
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>23</v>
@@ -1321,7 +1388,7 @@
         <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
@@ -1339,22 +1406,22 @@
         <v>19</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
       </c>
       <c r="AX5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA5" t="n">
         <v>25</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>24</v>
       </c>
       <c r="BB5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
         <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.772</v>
+        <v>0.753</v>
       </c>
       <c r="H6" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J6" t="n">
         <v>78</v>
       </c>
       <c r="K6" t="n">
-        <v>0.489</v>
+        <v>0.486</v>
       </c>
       <c r="L6" t="n">
         <v>7.4</v>
@@ -1422,52 +1489,52 @@
         <v>0.383</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P6" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.723</v>
+        <v>0.722</v>
       </c>
       <c r="R6" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T6" t="n">
         <v>42.6</v>
       </c>
       <c r="U6" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V6" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X6" t="n">
         <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.7</v>
+        <v>102.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1479,10 +1546,10 @@
         <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ6" t="n">
         <v>27</v>
@@ -1500,13 +1567,13 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR6" t="n">
         <v>27</v>
@@ -1518,7 +1585,7 @@
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
@@ -1536,7 +1603,7 @@
         <v>3</v>
       </c>
       <c r="BA6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -1574,43 +1641,43 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.675</v>
+        <v>0.663</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
       </c>
       <c r="I7" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J7" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M7" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="O7" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P7" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>10.2</v>
@@ -1619,10 +1686,10 @@
         <v>31.5</v>
       </c>
       <c r="T7" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U7" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="V7" t="n">
         <v>13</v>
@@ -1631,25 +1698,25 @@
         <v>7.6</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
         <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.2</v>
+        <v>101.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>4</v>
@@ -1664,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
         <v>14</v>
@@ -1679,7 +1746,7 @@
         <v>13</v>
       </c>
       <c r="AN7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1697,10 +1764,10 @@
         <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
         <v>3</v>
@@ -1709,7 +1776,7 @@
         <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1718,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -1774,34 +1841,34 @@
         <v>81.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.468</v>
+        <v>0.469</v>
       </c>
       <c r="L8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="P8" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R8" t="n">
         <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U8" t="n">
         <v>21</v>
@@ -1810,10 +1877,10 @@
         <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
         <v>5.3</v>
@@ -1822,31 +1889,31 @@
         <v>22.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.4</v>
+        <v>106.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ8" t="n">
         <v>17</v>
@@ -1861,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1876,7 +1943,7 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1885,7 +1952,7 @@
         <v>17</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -1938,13 +2005,13 @@
         <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>0.313</v>
+        <v>0.325</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1956,7 +2023,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
@@ -1965,22 +2032,22 @@
         <v>14.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="O9" t="n">
         <v>17.7</v>
       </c>
       <c r="P9" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.73</v>
+        <v>0.727</v>
       </c>
       <c r="R9" t="n">
         <v>12.9</v>
       </c>
       <c r="S9" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="T9" t="n">
         <v>40.3</v>
@@ -1992,7 +2059,7 @@
         <v>13.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
         <v>3.8</v>
@@ -2001,7 +2068,7 @@
         <v>4.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA9" t="n">
         <v>20.7</v>
@@ -2010,22 +2077,22 @@
         <v>93.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.6</v>
+        <v>-5.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>25</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>28</v>
@@ -2040,7 +2107,7 @@
         <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AN9" t="n">
         <v>30</v>
@@ -2061,16 +2128,16 @@
         <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU9" t="n">
         <v>26</v>
       </c>
       <c r="AV9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
         <v>27</v>
@@ -2079,10 +2146,10 @@
         <v>16</v>
       </c>
       <c r="AZ9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -2117,22 +2184,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>0.316</v>
+        <v>0.313</v>
       </c>
       <c r="H10" t="n">
         <v>48.1</v>
       </c>
       <c r="I10" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="J10" t="n">
         <v>86.5</v>
@@ -2144,19 +2211,19 @@
         <v>7.7</v>
       </c>
       <c r="M10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N10" t="n">
         <v>0.376</v>
       </c>
       <c r="O10" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R10" t="n">
         <v>9.199999999999999</v>
@@ -2168,7 +2235,7 @@
         <v>38.4</v>
       </c>
       <c r="U10" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V10" t="n">
         <v>14.8</v>
@@ -2177,7 +2244,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y10" t="n">
         <v>5</v>
@@ -2195,16 +2262,16 @@
         <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH10" t="n">
         <v>25</v>
@@ -2228,7 +2295,7 @@
         <v>3</v>
       </c>
       <c r="AO10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
@@ -2246,7 +2313,7 @@
         <v>30</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV10" t="n">
         <v>19</v>
@@ -2270,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -2299,52 +2366,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
         <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>0.519</v>
+        <v>0.513</v>
       </c>
       <c r="H11" t="n">
         <v>48.6</v>
       </c>
       <c r="I11" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J11" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L11" t="n">
         <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O11" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P11" t="n">
         <v>24.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.774</v>
+        <v>0.772</v>
       </c>
       <c r="R11" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T11" t="n">
         <v>42.2</v>
@@ -2353,31 +2420,31 @@
         <v>21.7</v>
       </c>
       <c r="V11" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="X11" t="n">
         <v>3.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
         <v>22.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>102.3</v>
+        <v>102</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>16</v>
@@ -2392,10 +2459,10 @@
         <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK11" t="n">
         <v>26</v>
@@ -2407,19 +2474,19 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
         <v>13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS11" t="n">
         <v>21</v>
@@ -2434,7 +2501,7 @@
         <v>17</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
         <v>26</v>
@@ -2443,13 +2510,13 @@
         <v>30</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
         <v>2</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -2499,34 +2566,34 @@
         <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="L12" t="n">
         <v>8.1</v>
       </c>
       <c r="M12" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="O12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
         <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R12" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S12" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
         <v>41.5</v>
@@ -2535,10 +2602,10 @@
         <v>21.2</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X12" t="n">
         <v>5.4</v>
@@ -2553,13 +2620,13 @@
         <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,13 +2638,13 @@
         <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK12" t="n">
         <v>28</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>15</v>
@@ -2598,7 +2665,7 @@
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
         <v>28</v>
@@ -2610,25 +2677,25 @@
         <v>19</v>
       </c>
       <c r="AU12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
         <v>16</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="n">
         <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>0.354</v>
+        <v>0.35</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
       </c>
       <c r="I13" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
         <v>5.9</v>
       </c>
       <c r="M13" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
         <v>16.7</v>
       </c>
       <c r="P13" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.732</v>
+        <v>0.729</v>
       </c>
       <c r="R13" t="n">
         <v>11.3</v>
@@ -2711,16 +2778,16 @@
         <v>30.4</v>
       </c>
       <c r="T13" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U13" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="V13" t="n">
         <v>15.7</v>
       </c>
       <c r="W13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X13" t="n">
         <v>5.7</v>
@@ -2729,28 +2796,28 @@
         <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AA13" t="n">
         <v>19.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.7</v>
+        <v>-6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF13" t="n">
         <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH13" t="n">
         <v>29</v>
@@ -2762,7 +2829,7 @@
         <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
         <v>20</v>
@@ -2774,7 +2841,7 @@
         <v>27</v>
       </c>
       <c r="AO13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP13" t="n">
         <v>25</v>
@@ -2786,34 +2853,34 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
         <v>28</v>
       </c>
       <c r="AW13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
         <v>2</v>
       </c>
       <c r="BA13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" t="n">
         <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.696</v>
+        <v>0.7</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
@@ -2872,22 +2939,22 @@
         <v>6.5</v>
       </c>
       <c r="M14" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O14" t="n">
         <v>18.5</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S14" t="n">
         <v>32.6</v>
@@ -2902,7 +2969,7 @@
         <v>13.3</v>
       </c>
       <c r="W14" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X14" t="n">
         <v>4.9</v>
@@ -2911,19 +2978,19 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB14" t="n">
         <v>101.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2938,10 +3005,10 @@
         <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK14" t="n">
         <v>17</v>
@@ -2959,13 +3026,13 @@
         <v>17</v>
       </c>
       <c r="AP14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
@@ -2986,7 +3053,7 @@
         <v>17</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -3042,10 +3109,10 @@
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J15" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="K15" t="n">
         <v>0.47</v>
@@ -3060,25 +3127,25 @@
         <v>0.341</v>
       </c>
       <c r="O15" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P15" t="n">
         <v>26.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R15" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S15" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T15" t="n">
         <v>43.5</v>
       </c>
       <c r="U15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
@@ -3090,22 +3157,22 @@
         <v>4.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA15" t="n">
         <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.8</v>
+        <v>102.5</v>
       </c>
       <c r="AC15" t="n">
         <v>-1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>17</v>
@@ -3117,13 +3184,13 @@
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
         <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
         <v>7</v>
@@ -3135,10 +3202,10 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP15" t="n">
         <v>5</v>
@@ -3156,7 +3223,7 @@
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
@@ -3165,13 +3232,13 @@
         <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
         <v>28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -3227,46 +3294,46 @@
         <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L16" t="n">
         <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P16" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
         <v>0.751</v>
       </c>
       <c r="R16" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S16" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T16" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U16" t="n">
         <v>18.9</v>
       </c>
       <c r="V16" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W16" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X16" t="n">
         <v>5.6</v>
@@ -3278,16 +3345,16 @@
         <v>20.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3299,7 +3366,7 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3311,22 +3378,22 @@
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN16" t="n">
         <v>20</v>
       </c>
       <c r="AO16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
         <v>21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
         <v>19</v>
@@ -3335,10 +3402,10 @@
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3356,13 +3423,13 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E17" t="n">
         <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>0.556</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I17" t="n">
         <v>37.2</v>
       </c>
       <c r="J17" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L17" t="n">
         <v>7.8</v>
       </c>
       <c r="M17" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O17" t="n">
         <v>15.4</v>
@@ -3436,25 +3503,25 @@
         <v>11.8</v>
       </c>
       <c r="S17" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T17" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U17" t="n">
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z17" t="n">
         <v>22.3</v>
@@ -3466,25 +3533,25 @@
         <v>97.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>13</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
         <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
@@ -3529,13 +3596,13 @@
         <v>18</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA17" t="n">
         <v>20</v>
@@ -3544,7 +3611,7 @@
         <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -3576,13 +3643,13 @@
         <v>80</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
-        <v>0.175</v>
+        <v>0.188</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
@@ -3591,67 +3658,67 @@
         <v>37.9</v>
       </c>
       <c r="J18" t="n">
-        <v>84.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M18" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O18" t="n">
         <v>17.4</v>
       </c>
       <c r="P18" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R18" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S18" t="n">
         <v>31.2</v>
       </c>
       <c r="T18" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U18" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V18" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X18" t="n">
         <v>3.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA18" t="n">
         <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.2</v>
+        <v>98</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3663,43 +3730,43 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
         <v>15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>26</v>
       </c>
       <c r="AM18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
       </c>
       <c r="AP18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
         <v>12</v>
       </c>
       <c r="AT18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU18" t="n">
         <v>24</v>
@@ -3708,13 +3775,13 @@
         <v>30</v>
       </c>
       <c r="AW18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -3773,49 +3840,49 @@
         <v>34.4</v>
       </c>
       <c r="J19" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="O19" t="n">
         <v>19.1</v>
       </c>
       <c r="P19" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q19" t="n">
         <v>0.78</v>
       </c>
       <c r="R19" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S19" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="T19" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="U19" t="n">
         <v>18.9</v>
       </c>
       <c r="V19" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W19" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
         <v>5.1</v>
@@ -3827,13 +3894,13 @@
         <v>20</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3845,7 +3912,7 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3860,19 +3927,19 @@
         <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN19" t="n">
         <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP19" t="n">
         <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
         <v>16</v>
@@ -3884,25 +3951,25 @@
         <v>28</v>
       </c>
       <c r="AU19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX19" t="n">
         <v>19</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>20</v>
       </c>
       <c r="AY19" t="n">
         <v>21</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
         <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>0.45</v>
+        <v>0.444</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,28 +4022,28 @@
         <v>38.6</v>
       </c>
       <c r="J20" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K20" t="n">
         <v>0.462</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O20" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P20" t="n">
         <v>20.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R20" t="n">
         <v>10.5</v>
@@ -3985,16 +4052,16 @@
         <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U20" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
         <v>3.7</v>
@@ -4012,10 +4079,10 @@
         <v>100</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4027,7 +4094,7 @@
         <v>20</v>
       </c>
       <c r="AH20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI20" t="n">
         <v>7</v>
@@ -4045,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -4054,40 +4121,40 @@
         <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
         <v>30</v>
       </c>
       <c r="AY20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -4122,34 +4189,34 @@
         <v>80</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
-        <v>0.363</v>
+        <v>0.35</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J21" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L21" t="n">
         <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O21" t="n">
         <v>16.7</v>
@@ -4170,7 +4237,7 @@
         <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V21" t="n">
         <v>14</v>
@@ -4191,13 +4258,13 @@
         <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>102.1</v>
+        <v>101.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.4</v>
+        <v>-3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4215,7 +4282,7 @@
         <v>12</v>
       </c>
       <c r="AJ21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK21" t="n">
         <v>20</v>
@@ -4227,10 +4294,10 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP21" t="n">
         <v>28</v>
@@ -4242,25 +4309,25 @@
         <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU21" t="n">
         <v>13</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW21" t="n">
         <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
         <v>9</v>
@@ -4272,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -4304,22 +4371,22 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6</v>
+        <v>0.613</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J22" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.461</v>
@@ -4328,16 +4395,16 @@
         <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="O22" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="P22" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q22" t="n">
         <v>0.805</v>
@@ -4346,13 +4413,13 @@
         <v>11.8</v>
       </c>
       <c r="S22" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T22" t="n">
         <v>43.6</v>
       </c>
       <c r="U22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
         <v>15</v>
@@ -4361,7 +4428,7 @@
         <v>8.1</v>
       </c>
       <c r="X22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y22" t="n">
         <v>4.7</v>
@@ -4373,22 +4440,22 @@
         <v>21.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
@@ -4397,10 +4464,10 @@
         <v>19</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL22" t="n">
         <v>25</v>
@@ -4421,10 +4488,10 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT22" t="n">
         <v>3</v>
@@ -4433,7 +4500,7 @@
         <v>23</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW22" t="n">
         <v>6</v>
@@ -4451,10 +4518,10 @@
         <v>10</v>
       </c>
       <c r="BB22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -4498,13 +4565,13 @@
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J23" t="n">
         <v>77.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L23" t="n">
         <v>10.2</v>
@@ -4513,34 +4580,34 @@
         <v>27.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.372</v>
+        <v>0.375</v>
       </c>
       <c r="O23" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="P23" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
         <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>33.5</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V23" t="n">
         <v>14.1</v>
       </c>
       <c r="W23" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X23" t="n">
         <v>5.6</v>
@@ -4552,7 +4619,7 @@
         <v>19.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB23" t="n">
         <v>102.3</v>
@@ -4561,7 +4628,7 @@
         <v>7.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4573,7 +4640,7 @@
         <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>25</v>
@@ -4591,16 +4658,16 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR23" t="n">
         <v>26</v>
@@ -4633,7 +4700,7 @@
         <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
         <v>1</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -4680,31 +4747,31 @@
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J24" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0.459</v>
       </c>
       <c r="L24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M24" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O24" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P24" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R24" t="n">
         <v>11.6</v>
@@ -4713,13 +4780,13 @@
         <v>29.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V24" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W24" t="n">
         <v>8.199999999999999</v>
@@ -4740,10 +4807,10 @@
         <v>97.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.7</v>
+        <v>-3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>24</v>
@@ -4758,7 +4825,7 @@
         <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ24" t="n">
         <v>15</v>
@@ -4770,13 +4837,13 @@
         <v>21</v>
       </c>
       <c r="AM24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
         <v>27</v>
@@ -4806,7 +4873,7 @@
         <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="n">
         <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>0.646</v>
+        <v>0.65</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
@@ -4865,37 +4932,37 @@
         <v>40.8</v>
       </c>
       <c r="J25" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="L25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.41</v>
+        <v>0.411</v>
       </c>
       <c r="O25" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P25" t="n">
         <v>25.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R25" t="n">
         <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U25" t="n">
         <v>23.4</v>
@@ -4910,7 +4977,7 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z25" t="n">
         <v>20.9</v>
@@ -4925,16 +4992,16 @@
         <v>4.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH25" t="n">
         <v>25</v>
@@ -4943,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK25" t="n">
         <v>2</v>
@@ -4958,7 +5025,7 @@
         <v>1</v>
       </c>
       <c r="AO25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP25" t="n">
         <v>9</v>
@@ -4970,28 +5037,28 @@
         <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW25" t="n">
         <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -5044,22 +5111,22 @@
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
         <v>16.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.351</v>
+        <v>0.355</v>
       </c>
       <c r="O26" t="n">
         <v>19.6</v>
@@ -5068,49 +5135,49 @@
         <v>24.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="R26" t="n">
         <v>11.2</v>
       </c>
       <c r="S26" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T26" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="U26" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V26" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="W26" t="n">
         <v>6.4</v>
       </c>
       <c r="X26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y26" t="n">
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC26" t="n">
         <v>3.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF26" t="n">
         <v>10</v>
@@ -5128,16 +5195,16 @@
         <v>26</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO26" t="n">
         <v>8</v>
@@ -5158,19 +5225,19 @@
         <v>27</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
         <v>2</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>24</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>18</v>
@@ -5182,7 +5249,7 @@
         <v>21</v>
       </c>
       <c r="BC26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -5226,13 +5293,13 @@
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J27" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K27" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L27" t="n">
         <v>5.9</v>
@@ -5241,7 +5308,7 @@
         <v>16.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.351</v>
+        <v>0.348</v>
       </c>
       <c r="O27" t="n">
         <v>17.5</v>
@@ -5262,13 +5329,13 @@
         <v>42.7</v>
       </c>
       <c r="U27" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V27" t="n">
         <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X27" t="n">
         <v>4.5</v>
@@ -5283,16 +5350,16 @@
         <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.2</v>
+        <v>-4.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
         <v>26</v>
@@ -5313,13 +5380,13 @@
         <v>19</v>
       </c>
       <c r="AL27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="n">
         <v>19</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>24</v>
@@ -5331,7 +5398,7 @@
         <v>28</v>
       </c>
       <c r="AR27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS27" t="n">
         <v>14</v>
@@ -5343,7 +5410,7 @@
         <v>20</v>
       </c>
       <c r="AV27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW27" t="n">
         <v>22</v>
@@ -5361,7 +5428,7 @@
         <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -5408,31 +5475,31 @@
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J28" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.473</v>
       </c>
       <c r="L28" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M28" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.362</v>
+        <v>0.359</v>
       </c>
       <c r="O28" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P28" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R28" t="n">
         <v>10.8</v>
@@ -5447,10 +5514,10 @@
         <v>22.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W28" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X28" t="n">
         <v>4.7</v>
@@ -5459,22 +5526,22 @@
         <v>5.1</v>
       </c>
       <c r="Z28" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AA28" t="n">
         <v>20.4</v>
       </c>
-      <c r="AA28" t="n">
-        <v>20.5</v>
-      </c>
       <c r="AB28" t="n">
-        <v>101.4</v>
+        <v>101.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF28" t="n">
         <v>10</v>
@@ -5483,10 +5550,10 @@
         <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
         <v>18</v>
@@ -5501,19 +5568,19 @@
         <v>11</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>23</v>
       </c>
       <c r="AR28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS28" t="n">
         <v>6</v>
@@ -5522,19 +5589,19 @@
         <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ28" t="n">
         <v>13</v>
@@ -5543,7 +5610,7 @@
         <v>19</v>
       </c>
       <c r="BB28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -5590,13 +5657,13 @@
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J29" t="n">
         <v>81</v>
       </c>
       <c r="K29" t="n">
-        <v>0.481</v>
+        <v>0.479</v>
       </c>
       <c r="L29" t="n">
         <v>6.3</v>
@@ -5605,31 +5672,31 @@
         <v>17.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.37</v>
+        <v>0.367</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P29" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="n">
         <v>0.764</v>
       </c>
       <c r="R29" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U29" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="V29" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W29" t="n">
         <v>5.7</v>
@@ -5638,22 +5705,22 @@
         <v>4.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>103.8</v>
+        <v>103.7</v>
       </c>
       <c r="AC29" t="n">
         <v>-2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>19</v>
@@ -5665,13 +5732,13 @@
         <v>19</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
         <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
         <v>5</v>
@@ -5686,25 +5753,25 @@
         <v>6</v>
       </c>
       <c r="AO29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP29" t="n">
         <v>8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR29" t="n">
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
         <v>7</v>
@@ -5713,10 +5780,10 @@
         <v>30</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E30" t="n">
         <v>52</v>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5778,25 +5845,25 @@
         <v>80.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.493</v>
+        <v>0.492</v>
       </c>
       <c r="L30" t="n">
         <v>5.3</v>
       </c>
       <c r="M30" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O30" t="n">
         <v>20.2</v>
       </c>
       <c r="P30" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="R30" t="n">
         <v>10.6</v>
@@ -5823,7 +5890,7 @@
         <v>5.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA30" t="n">
         <v>22.2</v>
@@ -5832,10 +5899,10 @@
         <v>104.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>5</v>
@@ -5895,10 +5962,10 @@
         <v>4</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
@@ -5942,94 +6009,94 @@
         <v>80</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3</v>
+        <v>0.313</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K31" t="n">
         <v>0.448</v>
       </c>
       <c r="L31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.354</v>
+        <v>0.35</v>
       </c>
       <c r="O31" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P31" t="n">
         <v>23.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.761</v>
+        <v>0.764</v>
       </c>
       <c r="R31" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U31" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V31" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W31" t="n">
         <v>6</v>
       </c>
       <c r="X31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA31" t="n">
         <v>20.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
         <v>23</v>
@@ -6038,7 +6105,7 @@
         <v>16</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>24</v>
@@ -6047,7 +6114,7 @@
         <v>23</v>
       </c>
       <c r="AN31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO31" t="n">
         <v>23</v>
@@ -6056,22 +6123,22 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW31" t="n">
         <v>28</v>
@@ -6080,7 +6147,7 @@
         <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AZ31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-12-2009-10</t>
+          <t>2010-04-12</t>
         </is>
       </c>
     </row>
